--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3887" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3658" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -444,33 +444,220 @@
     <t>Observation.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Auteur de l’observation</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.url</t>
+  </si>
+  <si>
+    <t>Observation.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Observation.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -478,6 +665,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -588,9 +778,6 @@
     <t>final</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/observation-status|4.0.1</t>
   </si>
   <si>
@@ -610,10 +797,6 @@
   </si>
   <si>
     <t>Observation.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Classification of  type of observation</t>
@@ -638,9 +821,6 @@
 value:coding.system}</t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
@@ -659,39 +839,16 @@
     <t>Observation.category.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.extension</t>
   </si>
   <si>
     <t>Observation.category.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.category:VSCat.coding</t>
@@ -1173,7 +1330,7 @@
 </t>
   </si>
   <si>
-    <t>Auteur</t>
+    <t>Who is responsible for the observation</t>
   </si>
   <si>
     <t>Who was responsible for asserting the observed value as "true".</t>
@@ -1192,245 +1349,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.performer.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
-</t>
-  </si>
-  <si>
-    <t>Auteur de l’observation</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode</t>
-  </si>
-  <si>
-    <t>typeCode</t>
-  </si>
-  <si>
-    <t>Type de participation</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
-</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Observation.performer.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>Observation.performer.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>Observation.performer.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>Observation.performer.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -2304,11 +2222,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP101"/>
+  <dimension ref="A1:AP95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.44921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.80859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3325,7 +3243,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3344,17 +3262,15 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -3391,16 +3307,14 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>143</v>
@@ -3427,7 +3341,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3441,43 +3355,41 @@
         <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3525,7 +3437,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3534,7 +3446,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3549,7 +3461,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3558,12 +3470,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3571,33 +3483,31 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3645,34 +3555,34 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3680,18 +3590,18 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3703,21 +3613,19 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3753,19 +3661,19 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3777,19 +3685,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3800,21 +3708,23 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3823,20 +3733,18 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3885,7 +3793,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3897,19 +3805,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3918,12 +3826,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3931,35 +3839,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3968,7 +3872,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3983,11 +3887,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -4005,10 +3911,10 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -4017,22 +3923,22 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -4040,10 +3946,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4051,13 +3957,13 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>82</v>
@@ -4066,20 +3972,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -4103,29 +4005,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>162</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4137,7 +4041,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4149,25 +4053,23 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>82</v>
       </c>
@@ -4179,7 +4081,7 @@
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
@@ -4188,26 +4090,24 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>82</v>
@@ -4225,13 +4125,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4249,19 +4149,19 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>82</v>
@@ -4273,10 +4173,10 @@
         <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>201</v>
+        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>82</v>
@@ -4284,10 +4184,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4310,13 +4210,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>206</v>
+        <v>113</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4328,7 +4228,7 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>82</v>
@@ -4343,13 +4243,11 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4367,7 +4265,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4379,7 +4277,7 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -4391,7 +4289,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4402,21 +4300,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4428,17 +4328,15 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4475,19 +4373,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4511,7 +4409,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4520,12 +4418,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4533,35 +4431,31 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>153</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>154</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4609,19 +4503,19 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>156</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4630,10 +4524,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>226</v>
+        <v>157</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4644,10 +4538,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>168</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4658,7 +4552,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4670,13 +4564,13 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4715,31 +4609,31 @@
         <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4751,7 +4645,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4762,21 +4656,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>230</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4788,16 +4682,16 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4805,7 +4699,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>82</v>
@@ -4835,31 +4729,31 @@
         <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -4871,7 +4765,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4880,12 +4774,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4893,41 +4787,37 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>237</v>
+        <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>82</v>
@@ -4969,7 +4859,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4990,10 +4880,10 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>136</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5004,18 +4894,20 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>93</v>
@@ -5027,20 +4919,18 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>139</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5089,19 +4979,19 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>162</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -5110,10 +5000,10 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5122,12 +5012,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5135,39 +5025,37 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>252</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>82</v>
@@ -5209,7 +5097,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>255</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5221,7 +5109,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5230,10 +5118,10 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>257</v>
+        <v>157</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5244,10 +5132,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5258,7 +5146,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5267,21 +5155,19 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>260</v>
+        <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>261</v>
+        <v>140</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>262</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5317,31 +5203,31 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>162</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5350,10 +5236,10 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>265</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5364,10 +5250,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>266</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>267</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5375,7 +5261,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>93</v>
@@ -5387,29 +5273,27 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>268</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>269</v>
+        <v>171</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>270</v>
+        <v>172</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5451,10 +5335,10 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>93</v>
@@ -5463,7 +5347,7 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5472,10 +5356,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>274</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>275</v>
+        <v>136</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5486,10 +5370,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>276</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>277</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5509,23 +5393,19 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>278</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5573,7 +5453,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>282</v>
+        <v>182</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5594,10 +5474,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5606,16 +5486,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>285</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>285</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5625,35 +5505,33 @@
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>287</v>
+        <v>171</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>288</v>
+        <v>172</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>82</v>
@@ -5671,13 +5549,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>292</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5695,7 +5573,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>285</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>93</v>
@@ -5707,33 +5585,33 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>297</v>
+        <v>136</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>298</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5744,7 +5622,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5756,13 +5634,13 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5813,7 +5691,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5825,7 +5703,7 @@
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5837,7 +5715,7 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>82</v>
@@ -5848,14 +5726,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>204</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5868,24 +5746,26 @@
         <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5921,19 +5801,19 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5957,7 +5837,7 @@
         <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>210</v>
+        <v>136</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -5968,10 +5848,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>211</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>211</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5994,19 +5874,17 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -6043,17 +5921,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6068,19 +5948,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>82</v>
+        <v>216</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -6088,16 +5968,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>304</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -6116,19 +5994,17 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6177,7 +6053,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6192,16 +6068,16 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6212,21 +6088,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>306</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>307</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6235,18 +6111,20 @@
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6295,31 +6173,31 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>236</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6328,46 +6206,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>238</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>140</v>
+        <v>239</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6376,7 +6256,7 @@
         <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>82</v>
@@ -6391,58 +6271,56 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6450,10 +6328,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
+        <v>250</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6461,41 +6339,41 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6513,37 +6391,35 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>82</v>
@@ -6558,58 +6434,62 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>260</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="C36" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="D36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6633,13 +6513,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6657,13 +6537,13 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
@@ -6678,13 +6558,13 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>247</v>
+        <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6692,10 +6572,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>262</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>263</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6715,27 +6595,25 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>251</v>
+        <v>154</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>252</v>
+        <v>155</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>317</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6777,7 +6655,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>255</v>
+        <v>156</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6789,7 +6667,7 @@
         <v>82</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>82</v>
@@ -6798,10 +6676,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>256</v>
+        <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>257</v>
+        <v>157</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6812,21 +6690,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>319</v>
+        <v>265</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>82</v>
@@ -6835,21 +6713,21 @@
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
@@ -6885,31 +6763,31 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>263</v>
+        <v>162</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6918,10 +6796,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>264</v>
+        <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>265</v>
+        <v>157</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6930,12 +6808,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>321</v>
+        <v>269</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6943,13 +6821,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -6958,19 +6836,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7019,13 +6897,13 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>82</v>
@@ -7040,10 +6918,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7054,10 +6932,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>322</v>
+        <v>279</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7077,23 +6955,19 @@
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>278</v>
+        <v>154</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>281</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7141,7 +7015,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>282</v>
+        <v>156</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7153,7 +7027,7 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -7162,10 +7036,10 @@
         <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>283</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>284</v>
+        <v>157</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7174,48 +7048,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>324</v>
+        <v>138</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>325</v>
+        <v>266</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>326</v>
+        <v>267</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7251,57 +7123,57 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>323</v>
+        <v>162</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>329</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>330</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>331</v>
+        <v>157</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>333</v>
+        <v>282</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>283</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7309,13 +7181,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>82</v>
@@ -7324,24 +7196,26 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>334</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>335</v>
+        <v>284</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>82</v>
+        <v>288</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>82</v>
@@ -7383,13 +7257,13 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>289</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
@@ -7404,13 +7278,13 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7418,14 +7292,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>292</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>339</v>
+        <v>293</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7444,20 +7318,18 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>341</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7505,7 +7377,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>339</v>
+        <v>297</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7520,19 +7392,19 @@
         <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>82</v>
@@ -7540,14 +7412,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7566,26 +7438,24 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>352</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>13</v>
+        <v>302</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>82</v>
@@ -7627,7 +7497,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>306</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7636,25 +7506,25 @@
         <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>357</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>359</v>
+        <v>307</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7662,10 +7532,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>362</v>
+        <v>309</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>310</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7688,18 +7558,18 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>363</v>
+        <v>153</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7747,7 +7617,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>362</v>
+        <v>314</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7768,24 +7638,24 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>367</v>
+        <v>315</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>368</v>
+        <v>316</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>317</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>370</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7799,7 +7669,7 @@
         <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>82</v>
@@ -7808,17 +7678,19 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>371</v>
+        <v>319</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>372</v>
+        <v>320</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O46" t="s" s="2">
-        <v>374</v>
+        <v>323</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7867,13 +7739,13 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
@@ -7882,19 +7754,19 @@
         <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>377</v>
+        <v>326</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>82</v>
@@ -7902,10 +7774,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>379</v>
+        <v>327</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7925,19 +7797,23 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>207</v>
+        <v>329</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7985,7 +7861,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>209</v>
+        <v>333</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7997,7 +7873,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8006,10 +7882,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>210</v>
+        <v>335</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8018,46 +7894,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>380</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>138</v>
+        <v>337</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>140</v>
+        <v>338</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>213</v>
+        <v>339</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -8081,73 +7959,71 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>216</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>210</v>
+        <v>348</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8156,7 +8032,7 @@
         <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8168,13 +8044,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>383</v>
+        <v>153</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>384</v>
+        <v>154</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>385</v>
+        <v>155</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8225,19 +8101,19 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>216</v>
+        <v>156</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8249,7 +8125,7 @@
         <v>82</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8260,21 +8136,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>352</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8286,15 +8162,17 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>207</v>
+        <v>266</v>
       </c>
       <c r="M50" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8331,31 +8209,31 @@
         <v>82</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8367,7 +8245,7 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8378,10 +8256,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8389,7 +8267,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>81</v>
@@ -8401,19 +8279,23 @@
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>391</v>
+        <v>271</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8449,19 +8331,17 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>354</v>
+      </c>
+      <c r="AC51" s="2"/>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8473,7 +8353,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8482,10 +8362,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8496,23 +8376,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>355</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>394</v>
+        <v>356</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8521,19 +8401,23 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>139</v>
+        <v>270</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>391</v>
+        <v>271</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
       </c>
@@ -8581,7 +8465,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8593,7 +8477,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8602,10 +8486,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>82</v>
+        <v>277</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8616,10 +8500,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>395</v>
+        <v>357</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>396</v>
+        <v>358</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8642,13 +8526,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>207</v>
+        <v>154</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8699,7 +8583,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>209</v>
+        <v>156</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8723,7 +8607,7 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>210</v>
+        <v>157</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>82</v>
@@ -8734,21 +8618,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
+        <v>360</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8760,15 +8644,17 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>391</v>
+        <v>266</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8805,19 +8691,19 @@
         <v>82</v>
       </c>
       <c r="AB54" t="s" s="2">
-        <v>214</v>
+        <v>141</v>
       </c>
       <c r="AC54" t="s" s="2">
-        <v>215</v>
+        <v>161</v>
       </c>
       <c r="AD54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>216</v>
+        <v>162</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8841,7 +8727,7 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
@@ -8852,10 +8738,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>361</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>362</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8863,7 +8749,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
@@ -8875,27 +8761,29 @@
         <v>82</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>284</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>285</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>82</v>
@@ -8937,10 +8825,10 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>404</v>
+        <v>289</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
         <v>93</v>
@@ -8949,7 +8837,7 @@
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8958,10 +8846,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>136</v>
+        <v>291</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8972,10 +8860,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>365</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8995,18 +8883,20 @@
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>407</v>
+        <v>294</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9016,7 +8906,7 @@
         <v>82</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>82</v>
@@ -9031,11 +8921,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -9053,7 +8945,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>411</v>
+        <v>297</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9074,10 +8966,10 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>82</v>
+        <v>298</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>136</v>
+        <v>299</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9088,14 +8980,12 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>412</v>
+        <v>366</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C57" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9113,25 +9003,27 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>414</v>
+        <v>302</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>392</v>
+        <v>303</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
-        <v>82</v>
+        <v>368</v>
       </c>
       <c r="S57" t="s" s="2">
         <v>82</v>
@@ -9173,19 +9065,19 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>216</v>
+        <v>306</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>82</v>
@@ -9194,10 +9086,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9208,10 +9100,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9231,19 +9123,21 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>206</v>
+        <v>153</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>207</v>
+        <v>311</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9291,7 +9185,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>209</v>
+        <v>314</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9303,7 +9197,7 @@
         <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>82</v>
@@ -9312,10 +9206,10 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>315</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9326,10 +9220,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>416</v>
+        <v>371</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9340,7 +9234,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9349,19 +9243,23 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>139</v>
+        <v>319</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>391</v>
+        <v>320</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9397,31 +9295,31 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>216</v>
+        <v>324</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>82</v>
@@ -9430,10 +9328,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>82</v>
+        <v>326</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9444,10 +9342,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>417</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>400</v>
+        <v>373</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9455,7 +9353,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
@@ -9467,27 +9365,29 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q60" s="2"/>
       <c r="R60" t="s" s="2">
-        <v>413</v>
+        <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
         <v>82</v>
@@ -9529,10 +9429,10 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>404</v>
+        <v>333</v>
       </c>
       <c r="AG60" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH60" t="s" s="2">
         <v>93</v>
@@ -9541,7 +9441,7 @@
         <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
@@ -9550,10 +9450,10 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>334</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>136</v>
+        <v>335</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
@@ -9562,12 +9462,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>418</v>
+        <v>374</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9575,31 +9475,35 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>191</v>
+        <v>375</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>376</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9647,7 +9551,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9662,19 +9566,19 @@
         <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>82</v>
+        <v>380</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>136</v>
+        <v>382</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9682,23 +9586,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>419</v>
+        <v>384</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="C62" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9707,18 +9609,20 @@
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>139</v>
+        <v>385</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9767,7 +9671,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>216</v>
+        <v>384</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9779,7 +9683,7 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9788,13 +9692,13 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>82</v>
+        <v>383</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>82</v>
@@ -9802,14 +9706,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>421</v>
+        <v>390</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9825,19 +9729,23 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>206</v>
+        <v>392</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>207</v>
+        <v>393</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>394</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9885,7 +9793,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>209</v>
+        <v>390</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9897,65 +9805,69 @@
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>82</v>
+        <v>397</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>210</v>
+        <v>399</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>139</v>
+        <v>403</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>391</v>
+        <v>13</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -9991,46 +9903,46 @@
         <v>82</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>216</v>
+        <v>401</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>144</v>
+        <v>408</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>82</v>
@@ -10038,10 +9950,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10049,7 +9961,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>93</v>
@@ -10061,19 +9973,19 @@
         <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>414</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10081,7 +9993,7 @@
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10123,10 +10035,10 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>93</v>
@@ -10135,7 +10047,7 @@
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10144,13 +10056,13 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>136</v>
+        <v>419</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>82</v>
+        <v>420</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>82</v>
@@ -10158,10 +10070,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10172,7 +10084,7 @@
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>82</v>
@@ -10181,19 +10093,21 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L66" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
@@ -10241,13 +10155,13 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>82</v>
@@ -10256,30 +10170,30 @@
         <v>105</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>136</v>
+        <v>428</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>82</v>
+        <v>429</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10287,39 +10201,41 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>107</v>
+        <v>431</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>401</v>
+        <v>432</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>402</v>
+        <v>432</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10361,45 +10277,45 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>136</v>
+        <v>438</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10410,10 +10326,10 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
@@ -10422,16 +10338,20 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>431</v>
+        <v>190</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>407</v>
+        <v>441</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10455,13 +10375,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10479,7 +10399,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10488,7 +10408,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>447</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10500,10 +10420,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>136</v>
+        <v>448</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10514,21 +10434,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10537,21 +10457,23 @@
         <v>82</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10575,13 +10497,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10599,16 +10521,16 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>436</v>
+        <v>449</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>437</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10617,27 +10539,27 @@
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>136</v>
+        <v>459</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10648,7 +10570,7 @@
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10657,21 +10579,23 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>462</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10695,13 +10619,13 @@
         <v>82</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10719,13 +10643,13 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
@@ -10740,10 +10664,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>136</v>
+        <v>468</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10754,10 +10678,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10777,19 +10701,19 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10815,13 +10739,13 @@
         <v>82</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>82</v>
+        <v>475</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10839,7 +10763,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10857,27 +10781,27 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>82</v>
+        <v>476</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>451</v>
+        <v>480</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10897,21 +10821,23 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>452</v>
+        <v>481</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>453</v>
+        <v>482</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -10935,13 +10861,13 @@
         <v>82</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>82</v>
@@ -10959,7 +10885,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10980,10 +10906,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>136</v>
+        <v>488</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10992,12 +10918,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11008,32 +10934,30 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>457</v>
+        <v>490</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>458</v>
+        <v>491</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>458</v>
+        <v>492</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>460</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11081,7 +11005,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>456</v>
+        <v>489</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11090,7 +11014,7 @@
         <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>461</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -11099,27 +11023,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>462</v>
+        <v>494</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>463</v>
+        <v>495</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>464</v>
+        <v>496</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>465</v>
+        <v>497</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11133,7 +11057,7 @@
         <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>82</v>
@@ -11142,20 +11066,18 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>191</v>
+        <v>499</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>467</v>
+        <v>500</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>468</v>
+        <v>501</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>470</v>
-      </c>
+        <v>502</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11179,13 +11101,13 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>471</v>
+        <v>82</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11203,7 +11125,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>466</v>
+        <v>498</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11212,7 +11134,7 @@
         <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>105</v>
@@ -11221,31 +11143,31 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>136</v>
+        <v>504</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>474</v>
+        <v>505</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -11264,19 +11186,19 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>191</v>
+        <v>508</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>478</v>
+        <v>510</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>479</v>
+        <v>511</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>480</v>
+        <v>512</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11301,13 +11223,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>291</v>
+        <v>82</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11325,7 +11247,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>475</v>
+        <v>507</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11337,33 +11259,33 @@
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>105</v>
+        <v>513</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>483</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>484</v>
+        <v>514</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>485</v>
+        <v>515</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>486</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>487</v>
+        <v>516</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11374,7 +11296,7 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11386,20 +11308,16 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>488</v>
+        <v>153</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>489</v>
+        <v>154</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11447,19 +11365,19 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>487</v>
+        <v>156</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11468,10 +11386,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>494</v>
+        <v>157</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11482,21 +11400,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
@@ -11508,16 +11426,16 @@
         <v>82</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>496</v>
+        <v>266</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>497</v>
+        <v>267</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>498</v>
+        <v>208</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11543,13 +11461,13 @@
         <v>82</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>82</v>
@@ -11567,80 +11485,80 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>495</v>
+        <v>162</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>504</v>
+        <v>157</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>505</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>509</v>
+        <v>208</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>510</v>
+        <v>209</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11665,13 +11583,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>512</v>
+        <v>82</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11689,19 +11607,19 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>82</v>
@@ -11710,10 +11628,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>514</v>
+        <v>136</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11724,10 +11642,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11750,17 +11668,15 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>519</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11809,7 +11725,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11818,7 +11734,7 @@
         <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>105</v>
@@ -11827,27 +11743,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11870,17 +11786,15 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11929,7 +11843,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11938,7 +11852,7 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>82</v>
+        <v>527</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -11947,27 +11861,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11978,7 +11892,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11990,7 +11904,7 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>534</v>
+        <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
         <v>535</v>
@@ -12027,13 +11941,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>540</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12051,31 +11965,31 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>539</v>
+        <v>105</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>541</v>
+        <v>459</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12086,10 +12000,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12100,7 +12014,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12112,16 +12026,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>207</v>
+        <v>544</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>545</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12145,13 +12063,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12169,31 +12087,31 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>209</v>
+        <v>543</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>541</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>210</v>
+        <v>459</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12204,21 +12122,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12230,18 +12148,18 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>139</v>
+        <v>551</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>140</v>
+        <v>552</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O83" s="2"/>
+        <v>553</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>554</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12289,19 +12207,19 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>216</v>
+        <v>550</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
@@ -12313,7 +12231,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>210</v>
+        <v>555</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12324,46 +12242,42 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>545</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12411,19 +12325,19 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12432,10 +12346,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>82</v>
+        <v>528</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>136</v>
+        <v>559</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12444,12 +12358,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12457,30 +12371,32 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>563</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
@@ -12529,16 +12445,16 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>105</v>
@@ -12550,10 +12466,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12564,10 +12480,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12578,7 +12494,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12587,18 +12503,20 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>570</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>571</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12647,16 +12565,16 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
         <v>105</v>
@@ -12668,10 +12586,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12680,12 +12598,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12696,31 +12614,31 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>191</v>
+        <v>508</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12745,13 +12663,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>565</v>
+        <v>82</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>566</v>
+        <v>82</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12769,31 +12687,31 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>105</v>
+        <v>577</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>485</v>
+        <v>579</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12804,10 +12722,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12818,7 +12736,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12830,20 +12748,16 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>570</v>
+        <v>154</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -12867,13 +12781,13 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>574</v>
+        <v>82</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
@@ -12891,31 +12805,31 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>569</v>
+        <v>156</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>567</v>
+        <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>485</v>
+        <v>157</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12926,21 +12840,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
@@ -12952,18 +12866,18 @@
         <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>577</v>
+        <v>138</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>578</v>
+        <v>266</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13011,19 +12925,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>576</v>
+        <v>162</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13035,7 +12949,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>581</v>
+        <v>157</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13053,35 +12967,39 @@
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>82</v>
+        <v>519</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>206</v>
+        <v>138</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>583</v>
+        <v>520</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+        <v>521</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13129,19 +13047,19 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>582</v>
+        <v>522</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>82</v>
@@ -13150,10 +13068,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>585</v>
+        <v>136</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13164,10 +13082,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13178,7 +13096,7 @@
         <v>93</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>94</v>
@@ -13190,18 +13108,20 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="O91" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="L91" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13225,13 +13145,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>82</v>
+        <v>344</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13249,13 +13169,13 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>82</v>
@@ -13267,27 +13187,27 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>82</v>
+        <v>588</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>591</v>
+        <v>347</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>592</v>
+        <v>348</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13298,10 +13218,10 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>82</v>
@@ -13310,18 +13230,20 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>594</v>
+        <v>431</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="O92" s="2"/>
+        <v>592</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>434</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13345,13 +13267,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>594</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13369,16 +13291,16 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>105</v>
@@ -13387,27 +13309,27 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>591</v>
+        <v>437</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>598</v>
+        <v>438</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13418,7 +13340,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>94</v>
@@ -13427,22 +13349,22 @@
         <v>82</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>534</v>
+        <v>190</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="M93" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>601</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>602</v>
+        <v>444</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13467,13 +13389,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13491,19 +13413,19 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>82</v>
+        <v>601</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>603</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
@@ -13512,10 +13434,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>604</v>
+        <v>136</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>605</v>
+        <v>448</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13526,21 +13448,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>82</v>
@@ -13552,16 +13474,20 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>207</v>
+        <v>451</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13585,13 +13511,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>82</v>
+        <v>455</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>82</v>
+        <v>456</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13609,49 +13535,49 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>209</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>210</v>
+        <v>459</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>82</v>
+        <v>460</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13670,18 +13596,20 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>140</v>
+        <v>604</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>213</v>
+        <v>605</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13729,7 +13657,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>216</v>
+        <v>603</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13741,7 +13669,7 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13750,752 +13678,20 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>210</v>
+        <v>515</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP101" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP101">
+  <autoFilter ref="A1:AP95">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14505,7 +13701,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI100">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-vital-signs-panel-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
